--- a/resources/tools/wordlist_E-J/lessons/lesson-20.xlsx
+++ b/resources/tools/wordlist_E-J/lessons/lesson-20.xlsx
@@ -431,240 +431,240 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>that way (polite)</t>
+          <t>animation</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>あちら</t>
+          <t>アニメ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>animation</t>
+          <t>novel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>アニメ</t>
+          <t>小説|しょうせつ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>space alien</t>
+          <t>hobby; pastime</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>宇宙人|うちゅうじん</t>
+          <t>趣味|しゅみ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sound</t>
+          <t>moon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>音|おと</t>
+          <t>月|つき</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rice ball</t>
+          <t>space alien</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>おにぎり</t>
+          <t>宇宙人|うちゅうじん</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>our person in charge</t>
+          <t>(hand) fan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>係の者|かかりのもの</t>
+          <t>扇子|せんす</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corner</t>
+          <t>sneakers</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>角|かど</t>
+          <t>スニーカー</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>airport</t>
+          <t>headphones</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>空港|くうこう</t>
+          <t>ヘッドホン</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>letter; character</t>
+          <t>rice ball</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>字|じ</t>
+          <t>おにぎり</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>branch office</t>
+          <t>animal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>支店|してん</t>
+          <t>動物|どうぶつ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hobby; pastime</t>
+          <t>that way (polite)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>趣味|しゅみ</t>
+          <t>あちら</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>novel</t>
+          <t>our person in charge</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>小説|しょうせつ</t>
+          <t>係の者|かかりのもの</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>traffic light</t>
+          <t>(someone's) house/home</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>信号|しんごう</t>
+          <t>お宅|おたく</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sneakers</t>
+          <t>...shop</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>スニーカー</t>
+          <t>～屋|～や</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fan</t>
+          <t>branch office</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>扇子|せんす</t>
+          <t>支店|してん</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>moon</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>月|つき</t>
+          <t>ドイツ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>electronic dictionary</t>
+          <t>traffic light</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>電子辞書|でんしじしょ</t>
+          <t>信号|しんごう</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>corner</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ドイツ</t>
+          <t>角|かど</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>high heels</t>
+          <t>letter; character</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ハイヒール</t>
+          <t>字|じ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>...shop</t>
+          <t>sound</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>～屋|～や</t>
+          <t>音|おと</t>
         </is>
       </c>
     </row>
@@ -695,144 +695,144 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>extra-modest expression for する</t>
+          <t>mysterious</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>致す|いたす</t>
+          <t>不思議|ふしぎ（な）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>extra-modest exp. for たべる and のむ/humble exp. for もらう</t>
+          <t>extra-modest expression for いる</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>頂く|いただく</t>
+          <t>おる</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>to humbly visit; to humbly ask</t>
+          <t>extra-modest expression for いく and くる</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>伺う|うかがう</t>
+          <t>参る|まいる</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>extra-modest expression for いる</t>
+          <t>extra-modest expression for いう</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>おる</t>
+          <t>申す|もうす</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>extra-modest expression for ある</t>
+          <t>extra-modest expression for する</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ござる</t>
+          <t>致す|いたす</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>extra-modest expression for ～ている</t>
+          <t>extra-modest exp. for たべる and のむ/humble exp. for もらう</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>～ておる</t>
+          <t>頂く|いただく</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>extra-modest expression for です</t>
+          <t>extra-modest expression for ある</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>～でござる</t>
+          <t>ござる</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>extra-modest expression for いく and くる</t>
+          <t>extra-modest expression for ～ている</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>参る|まいる</t>
+          <t>～ておる</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>to turn (right/left)</t>
+          <t>extra-modest expression for です</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>曲がる|まがる</t>
+          <t>～でござる</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>extra-modest expression for いう</t>
+          <t>(1) to humbly visit (place に); (2) to humbly ask (person に)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>申す|もうす</t>
+          <t>伺う|うかがう</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>to return; to come back</t>
+          <t>to turn (right/left) (corner を direction に)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>戻る|もどる</t>
+          <t>曲がる|まがる</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>to be audible</t>
+          <t>to return; to come back (～に)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>聞こえる|きこえる</t>
+          <t>戻る|もどる</t>
         </is>
       </c>
     </row>
@@ -851,144 +851,144 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>to convey (message)</t>
+          <t>to be audible (～が)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>伝える|つたえる</t>
+          <t>聞こえる|きこえる</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>to keep (someone) waiting</t>
+          <t>to convey message (person に)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>待たせる|またせる</t>
+          <t>伝える|つたえる</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>to exchange</t>
+          <t>to keep (someone) waiting (～を)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>交換する|こうかんする</t>
+          <t>待たせる|またせる</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>to lead a life</t>
+          <t>to continue (～を)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>生活する|せいかつする</t>
+          <t>続ける|つづける</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>to return (merchandise)</t>
+          <t>to exchange (X と Y を)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>返品する|へんぴんする</t>
+          <t>交換する|こうかんする</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Oh!</t>
+          <t>to return (merchandise) (～を)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>おや？</t>
+          <t>返品する|へんぴんする</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>...th floor</t>
+          <t>to lead a life</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>～階|～かい</t>
+          <t>生活する|せいかつする</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Certainly.</t>
+          <t>...th floor</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>かしこまりました</t>
+          <t>～階|～かい</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>I am not sure,...</t>
+          <t>first floor</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>さあ</t>
+          <t>一階|いっかい</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>I'm very sorry.</t>
+          <t>X like...</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>失礼しました|しつれいしました</t>
+          <t>～みたいなX</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>a few seconds</t>
+          <t>again</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>少々|しょうしょう</t>
+          <t>また</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>if that is the case,...</t>
+          <t>well then (polite)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>それでは</t>
+          <t>では</t>
         </is>
       </c>
     </row>
@@ -1019,48 +1019,48 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>again</t>
+          <t>if it is okay (polite)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>また</t>
+          <t>よろしかったら</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>X such as...</t>
+          <t>Certainly.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>～みたいなX</t>
+          <t>かしこまりました</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>You have my apologies.</t>
+          <t>I'm very sorry.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>申し訳ありません|もうしわけありません</t>
+          <t>失礼しました|しつれいしました</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>if it is okay (polite)</t>
+          <t>You have my apologies.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>よろしかったら</t>
+          <t>申し訳ありません|もうしわけありません</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>smile</t>
+          <t>smile; smiling face</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
